--- a/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:27:00+00:00</t>
+    <t>2026-04-24T08:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
